--- a/1_Data/Hu_YQ_2026_ChinaSciData/Exp2/Codebook_Hu_YQ_2026_ChinaSciData_Exp2_Clean.xlsx
+++ b/1_Data/Hu_YQ_2026_ChinaSciData/Exp2/Codebook_Hu_YQ_2026_ChinaSciData_Exp2_Clean.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t xml:space="preserve">Variable_name</t>
   </si>
@@ -32,223 +32,163 @@
     <t xml:space="preserve">Participant ID</t>
   </si>
   <si>
-    <t xml:space="preserve">6001 - 6036</t>
+    <t xml:space="preserve">11001-11011; 12001-12010; 21001-21003; 22001-22002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categorical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Between-subjects training group (2nd ID digit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matching-first; nonmatching-first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session / training time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baseline; training1; training2; training3; training4; training5; training6; training7; formal (= post-test)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">self-matching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trial phase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">practice; main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trial type: Matching (shape-label consistent) / Nonmatching (inconsistent) / filler (no-identity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matching; Nonmatching; filler (no-identity trial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shape stimulus (shape-label correspondence counterbalanced by ID parity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">circle; square</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shape_Origin_Identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original-language identity of the shape stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">self; other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shape_English_Identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English identity of the shape stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self; Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shape_Standardized_Identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standardized identity (6-category)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self; Stranger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label word presented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自我 (self); 他人 (other); 白栽; 地入 (filler pseudo-words)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label_Origin_Identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original-language identity of the label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自我; 他人; 白栽; 地入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label_English_Identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English identity of the label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self; Other; Filler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label_Standardized_Identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self; Stranger; Filler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CorrResponse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct response key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p; o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual key response; NA = no response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p; o; NA (no response)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RT_ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaction time in milliseconds; NA = no response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ms; NA = no response</t>
   </si>
   <si>
     <t xml:space="preserve">Numerical</t>
   </si>
   <si>
-    <t xml:space="preserve">Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Between-subjects group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">control; depression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Categorical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session number (one complete experimental participation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Association/task type (whether the association involves a self-referential identity)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">self-matching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trial phase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">main; practice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block number (NA for practice trials)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trial number within block / list cycle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whether the presented shape-label pair matches the learned association</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matching; Nonmatching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presented shape stimulus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_eh.bmp; c_en.bmp; c_es.bmp; c.bmp; hc_eh.bmp; hc_en.bmp; hc_es.bmp; hc.bmp; vc_eh.bmp; vc_en.bmp; vc_es.bmp; vc.bmp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shape_Origin_Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identity of the shape in its original form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">friend; self; stranger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shape_English_Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English translation of the shape identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friend; Self; Stranger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shape_Standardized_Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canonical standardized identity of the shape (6-category vocabulary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Close; Self; Stranger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presented label stimulus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生人; 自己; 朋友</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label_Origin_Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identity of the label in its original form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label_English_Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English translation of the label identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label_Standardized_Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canonical standardized identity of the label (6-category vocabulary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CorrResponse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correct response key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m; n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Response</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Participant's response key (NA = no response)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m; n; NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RT_ms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reaction time in milliseconds (NA = no response)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">milliseconds (NA = no response)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ACC</t>
   </si>
   <si>
-    <t xml:space="preserve">Accuracy: 1 = correct, 0 = incorrect (wrong key), NA = no response</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (correct); 0 (incorrect); NA (no response)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selfpic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Circle image assigned to the self identity (counterbalanced)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c; hc; vc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friendpic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Circle image assigned to the friend identity (counterbalanced)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strangerpic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Circle image assigned to the stranger identity (counterbalanced)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emotion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emotional expression of the shape stimulus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">control; happy; neutral; sad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrialList.Cycle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-Prime list cycle number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clock.StartTimeOfDay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trial start time of day (MM/DD/YY HH:MM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/21/15 19:58; 10/23/15 09:16; 10/23/15 14:54; 10/23/15 19:22; 10/24/15 09:39; 10/24/15 11:47; 10/24/15 14:18; 10/24/15 17:39; 10/24/15 19:38; 10/24/15 21:00; 10/25/15 08:34; 10/25/15 08:59; 10/25/15 10:40; 10/25/15 10:45; 10/25/15 15:31; 10/25/15 15:43; 10/25/15 19:15; 10/25/15 19:29; 10/26/15 08:44; 10/26/15 08:56; 10/26/15 10:51; 10/26/15 10:54; 10/26/15 14:15; 10/26/15 14:36; 10/26/15 20:29; 10/27/15 10:47; 10/29/15 08:18; 10/29/15 10:16; 10/29/15 10:32; 10/29/15 14:14; 10/29/15 14:16; 10/29/15 14:29; 10/29/15 19:11; 10/29/15 19:16; 10/29/15 19:23; 10/31/15 08:25; 10/31/15 08:43; 10/31/15 10:30; 10/31/15 14:22; 10/31/15 14:24</t>
+    <t xml:space="preserve">Accuracy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (correct); 0 (error); NA (no response)</t>
   </si>
 </sst>
 </file>
@@ -293,19 +233,6 @@
   </cellStyles>
   <dxfs count="0"/>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D27" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:D27"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="Variable_name"/>
-    <tableColumn id="2" name="Variable_description"/>
-    <tableColumn id="3" name="Variable_value"/>
-    <tableColumn id="4" name="Variable_category"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -629,18 +556,18 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -648,41 +575,41 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -690,13 +617,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -704,114 +631,114 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>28</v>
       </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>43</v>
       </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
         <v>45</v>
       </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s">
         <v>47</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>48</v>
       </c>
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -822,157 +749,42 @@
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-  <tableParts count="1">
-    <tablePart r:id="rId3"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/1_Data/Hu_YQ_2026_ChinaSciData/Exp2/Codebook_Hu_YQ_2026_ChinaSciData_Exp2_Clean.xlsx
+++ b/1_Data/Hu_YQ_2026_ChinaSciData/Exp2/Codebook_Hu_YQ_2026_ChinaSciData_Exp2_Clean.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t xml:space="preserve">Variable_name</t>
   </si>
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Participant ID</t>
+    <t xml:space="preserve">Participant ID (source folder name; the 2nd ID digit codes the training group)</t>
   </si>
   <si>
     <t xml:space="preserve">11001-11011; 12001-12010; 21001-21003; 22001-22002</t>
@@ -41,7 +41,7 @@
     <t xml:space="preserve">Group</t>
   </si>
   <si>
-    <t xml:space="preserve">Between-subjects training group (2nd ID digit)</t>
+    <t xml:space="preserve">Between-subjects training group (from the 2nd ID digit)</t>
   </si>
   <si>
     <t xml:space="preserve">matching-first; nonmatching-first</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Session</t>
   </si>
   <si>
-    <t xml:space="preserve">Session / training time point</t>
+    <t xml:space="preserve">Session = one lab visit / training time point; the nine sessions fall on distinct dates per participant (verified from the raw Date column)</t>
   </si>
   <si>
     <t xml:space="preserve">baseline; training1; training2; training3; training4; training5; training6; training7; formal (= post-test)</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">Task</t>
   </si>
   <si>
-    <t xml:space="preserve">Task type</t>
+    <t xml:space="preserve">Task: self-matching (matching-verification training with self/other shape-label pairs and filler pseudo-words). Task value is pending the database-wide Task-vocabulary survey</t>
   </si>
   <si>
     <t xml:space="preserve">self-matching</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Phase</t>
   </si>
   <si>
-    <t xml:space="preserve">Trial phase</t>
+    <t xml:space="preserve">Trial phase. Block and trial numbers are absent from the source exports - trial order is preserved by the row order within each session (open item, awaiting confirmation by the original author)</t>
   </si>
   <si>
     <t xml:space="preserve">practice; main</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">Matching</t>
   </si>
   <si>
-    <t xml:space="preserve">Trial type: Matching (shape-label consistent) / Nonmatching (inconsistent) / filler (no-identity)</t>
+    <t xml:space="preserve">Trial type: Matching (shape-label consistent) / Nonmatching (inconsistent) / filler (no-identity pseudo-word trial, kept as-is; registered exception, cf. Wu_2026_Chinaxiv)</t>
   </si>
   <si>
     <t xml:space="preserve">Matching; Nonmatching; filler (no-identity trial)</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Shape</t>
   </si>
   <si>
-    <t xml:space="preserve">Shape stimulus (shape-label correspondence counterbalanced by ID parity)</t>
+    <t xml:space="preserve">Shape stimulus (shape-label correspondence counterbalanced by ID parity: even ID self = circle / other = square, odd ID self = square / other = circle)</t>
   </si>
   <si>
     <t xml:space="preserve">circle; square</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Shape_Origin_Identity</t>
   </si>
   <si>
-    <t xml:space="preserve">Original-language identity of the shape stimulus</t>
+    <t xml:space="preserve">Original-language identity carried by the shape stimulus</t>
   </si>
   <si>
     <t xml:space="preserve">self; other</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">Shape_English_Identity</t>
   </si>
   <si>
-    <t xml:space="preserve">English identity of the shape stimulus</t>
+    <t xml:space="preserve">English form of Shape_Origin_Identity</t>
   </si>
   <si>
     <t xml:space="preserve">Self; Other</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">Shape_Standardized_Identity</t>
   </si>
   <si>
-    <t xml:space="preserve">Standardized identity (6-category)</t>
+    <t xml:space="preserve">Standardized identity (6-category vocabulary)</t>
   </si>
   <si>
     <t xml:space="preserve">Self; Stranger</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">Label</t>
   </si>
   <si>
-    <t xml:space="preserve">Label word presented</t>
+    <t xml:space="preserve">Label word presented (original language)</t>
   </si>
   <si>
     <t xml:space="preserve">自我 (self); 他人 (other); 白栽; 地入 (filler pseudo-words)</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">Label_Origin_Identity</t>
   </si>
   <si>
-    <t xml:space="preserve">Original-language identity of the label</t>
+    <t xml:space="preserve">Original-language identity of the presented label word</t>
   </si>
   <si>
     <t xml:space="preserve">自我; 他人; 白栽; 地入</t>
@@ -140,13 +140,16 @@
     <t xml:space="preserve">Label_English_Identity</t>
   </si>
   <si>
-    <t xml:space="preserve">English identity of the label</t>
+    <t xml:space="preserve">English form of the presented label word</t>
   </si>
   <si>
     <t xml:space="preserve">Self; Other; Filler</t>
   </si>
   <si>
     <t xml:space="preserve">Label_Standardized_Identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standardized identity of the presented label word (person identities by the 6-category vocabulary; Filler = no-identity pseudo-word trials, kept as-is, registered exception)</t>
   </si>
   <si>
     <t xml:space="preserve">Self; Stranger; Filler</t>
@@ -718,10 +721,10 @@
         <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -729,13 +732,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -743,13 +746,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -757,27 +760,27 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
